--- a/DirectX/Bin/Asset/Brotato/tables/Enemy.xlsx
+++ b/DirectX/Bin/Asset/Brotato/tables/Enemy.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\jglee\ASTR\AstrDX\DirectX\Bin\Asset\Brotato\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C565CC20-A8A9-4216-AAC5-DAA2413736FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F61DBA62-A290-4485-BF7A-2D7BED4E521C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="16440" windowHeight="28320" xr2:uid="{D120B664-9625-4DC7-9A8C-DD4CF0EBB165}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>ID</t>
     <phoneticPr fontId="18" type="noConversion"/>
@@ -110,7 +110,11 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>KnockbackResistPercent</t>
+    <t>KnockbackResist</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Behavior</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1083,10 +1087,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F041C6E9-5782-4583-B661-038F00A20FAE}">
-  <dimension ref="A1:U4"/>
+  <dimension ref="A1:V4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1103,55 +1107,58 @@
         <v>2</v>
       </c>
       <c r="F1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>22</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>18</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>14</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>15</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>16</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>17</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1164,14 +1171,11 @@
       <c r="E2">
         <v>0</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>10</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>5</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -1183,27 +1187,30 @@
         <v>0</v>
       </c>
       <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="N2">
+        <v>3</v>
+      </c>
+      <c r="O2">
         <v>100</v>
       </c>
-      <c r="M2">
-        <v>3</v>
-      </c>
-      <c r="N2">
-        <v>100</v>
-      </c>
-      <c r="O2">
+      <c r="P2">
         <v>20</v>
       </c>
-      <c r="P2">
+      <c r="Q2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>

--- a/DirectX/Bin/Asset/Brotato/tables/Enemy.xlsx
+++ b/DirectX/Bin/Asset/Brotato/tables/Enemy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\jglee\ASTR\AstrDX\DirectX\Bin\Asset\Brotato\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F61DBA62-A290-4485-BF7A-2D7BED4E521C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE4BF44C-71C4-4763-83D9-AD7611E3A62A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="16440" windowHeight="28320" xr2:uid="{D120B664-9625-4DC7-9A8C-DD4CF0EBB165}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>ID</t>
     <phoneticPr fontId="18" type="noConversion"/>
@@ -115,6 +115,14 @@
   </si>
   <si>
     <t>Behavior</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ColliderSizeX</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ColliderSizeY</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1087,10 +1095,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F041C6E9-5782-4583-B661-038F00A20FAE}">
-  <dimension ref="A1:V4"/>
+  <dimension ref="A1:X2"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1104,61 +1112,67 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>23</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>22</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>11</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>12</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>14</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>15</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" t="s">
         <v>16</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
         <v>17</v>
       </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1169,19 +1183,19 @@
         <v>21</v>
       </c>
       <c r="E2">
+        <v>140</v>
+      </c>
+      <c r="F2">
+        <v>140</v>
+      </c>
+      <c r="G2">
         <v>0</v>
       </c>
-      <c r="G2">
+      <c r="I2">
         <v>10</v>
       </c>
-      <c r="H2">
+      <c r="J2">
         <v>5</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -1190,29 +1204,25 @@
         <v>0</v>
       </c>
       <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
         <v>1</v>
       </c>
-      <c r="N2">
+      <c r="P2">
         <v>3</v>
       </c>
-      <c r="O2">
+      <c r="Q2">
         <v>100</v>
       </c>
-      <c r="P2">
+      <c r="R2">
         <v>20</v>
       </c>
-      <c r="Q2">
+      <c r="S2">
         <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/DirectX/Bin/Asset/Brotato/tables/Enemy.xlsx
+++ b/DirectX/Bin/Asset/Brotato/tables/Enemy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\jglee\ASTR\AstrDX\DirectX\Bin\Asset\Brotato\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE4BF44C-71C4-4763-83D9-AD7611E3A62A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F9A8588-AF0B-45AE-A7C3-5DF8EDAAC8E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="16440" windowHeight="28320" xr2:uid="{D120B664-9625-4DC7-9A8C-DD4CF0EBB165}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>ID</t>
     <phoneticPr fontId="18" type="noConversion"/>
@@ -123,6 +123,18 @@
   </si>
   <si>
     <t>ColliderSizeY</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>BabyAlien</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>entities/units/enemies/baby_alien/baby_alien_icon.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>entities/units/enemies/baby_alien/baby_alien.png</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1095,7 +1107,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F041C6E9-5782-4583-B661-038F00A20FAE}">
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:X3"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.3">
@@ -1222,6 +1234,65 @@
         <v>20</v>
       </c>
       <c r="S2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3">
+        <v>70</v>
+      </c>
+      <c r="F3">
+        <v>80</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>200</v>
+      </c>
+      <c r="L3">
+        <v>300</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3">
+        <v>0.6</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>1</v>
+      </c>
+      <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="R3">
+        <v>1</v>
+      </c>
+      <c r="S3">
         <v>1</v>
       </c>
     </row>
